--- a/mercato 26_2.xlsx
+++ b/mercato 26_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sint2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sint2\Desktop\sito fmto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{150EEFCD-45CA-4CFC-BB3B-CCB33165E4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA510F60-2B6F-4AD3-AB33-AC53F80C3469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99E1B42E-92D6-4452-B351-A7ED870CFFC3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="106">
   <si>
     <t>GIOCATORE</t>
   </si>
@@ -321,6 +321,39 @@
   </si>
   <si>
     <t>Henrikh MKHITARYAN</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>Definitivo</t>
+  </si>
+  <si>
+    <t>Obbligo di riscatto esercitato</t>
+  </si>
+  <si>
+    <t>Scambio</t>
+  </si>
+  <si>
+    <t>Clausola di riacquisto esercitata</t>
+  </si>
+  <si>
+    <t>Vendita diretta</t>
+  </si>
+  <si>
+    <t>Rinuncia alla clausola di riacquisto</t>
+  </si>
+  <si>
+    <t>Diritto di riscatto esercitato</t>
+  </si>
+  <si>
+    <t>Prestito oneroso</t>
   </si>
 </sst>
 </file>
@@ -692,15 +725,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6F8EC8-570C-45A6-A3F9-20FAD10EBF7E}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -710,8 +746,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -721,8 +766,17 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -732,8 +786,17 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -743,8 +806,17 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -754,8 +826,17 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -765,8 +846,14 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -776,8 +863,14 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -787,8 +880,14 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -798,8 +897,17 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -809,8 +917,17 @@
       <c r="C10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -820,8 +937,14 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -831,8 +954,14 @@
       <c r="C12" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -842,8 +971,17 @@
       <c r="C13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -853,8 +991,14 @@
       <c r="C14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -864,8 +1008,14 @@
       <c r="C15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -875,8 +1025,14 @@
       <c r="C16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -886,8 +1042,14 @@
       <c r="C17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -897,8 +1059,14 @@
       <c r="C18" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -908,8 +1076,14 @@
       <c r="C19" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -919,8 +1093,14 @@
       <c r="C20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -930,8 +1110,14 @@
       <c r="C21" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -941,8 +1127,14 @@
       <c r="C22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -952,8 +1144,17 @@
       <c r="C23" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -963,8 +1164,14 @@
       <c r="C24" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -974,8 +1181,17 @@
       <c r="C25" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -985,8 +1201,17 @@
       <c r="C26" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -996,8 +1221,17 @@
       <c r="C27" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1007,8 +1241,17 @@
       <c r="C28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -1018,8 +1261,14 @@
       <c r="C29" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -1029,8 +1278,14 @@
       <c r="C30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -1040,8 +1295,17 @@
       <c r="C31" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1051,8 +1315,17 @@
       <c r="C32" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -1062,8 +1335,17 @@
       <c r="C33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -1073,8 +1355,17 @@
       <c r="C34" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -1084,8 +1375,17 @@
       <c r="C35" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
@@ -1095,8 +1395,17 @@
       <c r="C36" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>56</v>
       </c>
@@ -1106,8 +1415,14 @@
       <c r="C37" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>56</v>
       </c>
@@ -1117,8 +1432,14 @@
       <c r="C38" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -1128,8 +1449,17 @@
       <c r="C39" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -1139,8 +1469,17 @@
       <c r="C40" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -1150,8 +1489,17 @@
       <c r="C41" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -1161,8 +1509,17 @@
       <c r="C42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>63</v>
       </c>
@@ -1172,8 +1529,17 @@
       <c r="C43" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>64</v>
       </c>
@@ -1183,8 +1549,17 @@
       <c r="C44" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>98</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -1194,8 +1569,17 @@
       <c r="C45" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -1205,8 +1589,17 @@
       <c r="C46" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -1216,8 +1609,17 @@
       <c r="C47" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -1227,8 +1629,17 @@
       <c r="C48" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -1238,8 +1649,17 @@
       <c r="C49" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -1249,8 +1669,17 @@
       <c r="C50" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -1260,8 +1689,17 @@
       <c r="C51" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>72</v>
       </c>
@@ -1271,8 +1709,17 @@
       <c r="C52" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>98</v>
+      </c>
+      <c r="E52">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -1282,8 +1729,17 @@
       <c r="C53" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>75</v>
       </c>
@@ -1293,8 +1749,17 @@
       <c r="C54" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>76</v>
       </c>
@@ -1304,8 +1769,17 @@
       <c r="C55" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>77</v>
       </c>
@@ -1315,8 +1789,17 @@
       <c r="C56" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>105</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -1326,8 +1809,17 @@
       <c r="C57" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>98</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>80</v>
       </c>
@@ -1337,8 +1829,17 @@
       <c r="C58" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>98</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -1348,8 +1849,17 @@
       <c r="C59" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -1359,8 +1869,17 @@
       <c r="C60" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>84</v>
       </c>
@@ -1370,8 +1889,17 @@
       <c r="C61" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>85</v>
       </c>
@@ -1381,8 +1909,17 @@
       <c r="C62" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>98</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>86</v>
       </c>
@@ -1392,8 +1929,17 @@
       <c r="C63" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
+        <v>98</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>88</v>
       </c>
@@ -1403,8 +1949,17 @@
       <c r="C64" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>89</v>
       </c>
@@ -1414,8 +1969,17 @@
       <c r="C65" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
+        <v>98</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>90</v>
       </c>
@@ -1425,8 +1989,17 @@
       <c r="C66" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>91</v>
       </c>
@@ -1436,8 +2009,17 @@
       <c r="C67" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" t="s">
+        <v>98</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>92</v>
       </c>
@@ -1447,8 +2029,17 @@
       <c r="C68" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68">
+        <v>5</v>
+      </c>
+      <c r="F68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>93</v>
       </c>
@@ -1458,8 +2049,17 @@
       <c r="C69" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" t="s">
+        <v>98</v>
+      </c>
+      <c r="E69">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -1468,6 +2068,15 @@
       </c>
       <c r="C70" t="s">
         <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70">
+        <v>8</v>
+      </c>
+      <c r="F70" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/mercato 26_2.xlsx
+++ b/mercato 26_2.xlsx
@@ -1,42 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sint2\Desktop\sito fmto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA510F60-2B6F-4AD3-AB33-AC53F80C3469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C38460-26A8-4A29-A286-282012E0C676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99E1B42E-92D6-4452-B351-A7ED870CFFC3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="420">
   <si>
     <t>GIOCATORE</t>
   </si>
@@ -47,6 +32,18 @@
     <t>CEDENTE</t>
   </si>
   <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>Robert ANDRICH</t>
   </si>
   <si>
@@ -56,6 +53,12 @@
     <t>LIPSIA</t>
   </si>
   <si>
+    <t>Definitivo</t>
+  </si>
+  <si>
+    <t>Obbligo di riscatto esercitato</t>
+  </si>
+  <si>
     <t>Takefusa KUBO</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t>NAPOLI</t>
   </si>
   <si>
+    <t>Scambio</t>
+  </si>
+  <si>
     <t>Facundo TORRES</t>
   </si>
   <si>
@@ -98,6 +104,12 @@
     <t>MANCHESTER UNITED</t>
   </si>
   <si>
+    <t>Clausola di riacquisto esercitata</t>
+  </si>
+  <si>
+    <t>Vendita diretta</t>
+  </si>
+  <si>
     <t>Domenico BERARDI</t>
   </si>
   <si>
@@ -164,6 +176,9 @@
     <t>LIVERPOOL</t>
   </si>
   <si>
+    <t>Rinuncia alla clausola di riacquisto</t>
+  </si>
+  <si>
     <t>Ferdi KADIOĞLU</t>
   </si>
   <si>
@@ -275,6 +290,9 @@
     <t>OLYMPIAKOS</t>
   </si>
   <si>
+    <t>Prestito oneroso</t>
+  </si>
+  <si>
     <t>Jean-Clair TODIBO</t>
   </si>
   <si>
@@ -323,43 +341,956 @@
     <t>Henrikh MKHITARYAN</t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>NOTE</t>
-  </si>
-  <si>
-    <t>Definitivo</t>
-  </si>
-  <si>
-    <t>Obbligo di riscatto esercitato</t>
-  </si>
-  <si>
-    <t>Scambio</t>
-  </si>
-  <si>
-    <t>Clausola di riacquisto esercitata</t>
-  </si>
-  <si>
-    <t>Vendita diretta</t>
-  </si>
-  <si>
-    <t>Rinuncia alla clausola di riacquisto</t>
-  </si>
-  <si>
-    <t>Diritto di riscatto esercitato</t>
-  </si>
-  <si>
-    <t>Prestito oneroso</t>
+    <t>Tim KLEINDIENST</t>
+  </si>
+  <si>
+    <t>Martin VITÍK</t>
+  </si>
+  <si>
+    <t>Luís Guilherme LIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Thijs DALLINGA</t>
+  </si>
+  <si>
+    <t>Mika BIERETH</t>
+  </si>
+  <si>
+    <t>Axel TAPE</t>
+  </si>
+  <si>
+    <t>ASTANA</t>
+  </si>
+  <si>
+    <t>Clausola di riacquisto</t>
+  </si>
+  <si>
+    <t>Mathías OLIVERA</t>
+  </si>
+  <si>
+    <t>Nicolas SEIWALD</t>
+  </si>
+  <si>
+    <t>Ian SUBIABRE</t>
+  </si>
+  <si>
+    <t>Bafodé DIAKITÉ</t>
+  </si>
+  <si>
+    <t>Alex TÓTH</t>
+  </si>
+  <si>
+    <t>Kerim ALAJBEGOVIĆ</t>
+  </si>
+  <si>
+    <t>Dango OUATTARA</t>
+  </si>
+  <si>
+    <t>Antonio RÜDIGER</t>
+  </si>
+  <si>
+    <t>Serhou GUIRASSY</t>
+  </si>
+  <si>
+    <t>Wílmar BARRIOS</t>
+  </si>
+  <si>
+    <t>BARCELONA</t>
+  </si>
+  <si>
+    <t>Antonín KINSKÝ</t>
+  </si>
+  <si>
+    <t>André ONANA</t>
+  </si>
+  <si>
+    <t>GLASGOW RANGERS</t>
+  </si>
+  <si>
+    <t>Tom ROTHE</t>
+  </si>
+  <si>
+    <t>Jack HINSHELWOOD</t>
+  </si>
+  <si>
+    <t>Oskar PIETUSZEWSKI</t>
+  </si>
+  <si>
+    <t>Pablo BARRIOS</t>
+  </si>
+  <si>
+    <t>Joan TINCRES</t>
+  </si>
+  <si>
+    <t>Luca LIPANI</t>
+  </si>
+  <si>
+    <t>Gianluca PRESTIANNI</t>
+  </si>
+  <si>
+    <t>Niklas BESTE</t>
+  </si>
+  <si>
+    <t>COPENAGHEN</t>
+  </si>
+  <si>
+    <t>Jack CLARKE</t>
+  </si>
+  <si>
+    <t>Rocco REITZ</t>
+  </si>
+  <si>
+    <t>Youri BAAS</t>
+  </si>
+  <si>
+    <t>Joshua ZIRKZEE</t>
+  </si>
+  <si>
+    <t>Leroy SANÉ</t>
+  </si>
+  <si>
+    <t>Jan OBLAK</t>
+  </si>
+  <si>
+    <t>Oleksandr ZINCHENKO</t>
+  </si>
+  <si>
+    <t>Matheus REIS DE LIMA</t>
+  </si>
+  <si>
+    <t>Ángel DI MARÍA</t>
+  </si>
+  <si>
+    <t>Jon ARAMBURU</t>
+  </si>
+  <si>
+    <t>STELLA ROSSA</t>
+  </si>
+  <si>
+    <t>Marc CASADÓ</t>
+  </si>
+  <si>
+    <t>Andreas SCHJELDERUP</t>
+  </si>
+  <si>
+    <t>Evan FERGUSON</t>
+  </si>
+  <si>
+    <t>MILAN</t>
+  </si>
+  <si>
+    <t>James MCATEE</t>
+  </si>
+  <si>
+    <t>Raphael CAVALCANTE VEIGA</t>
+  </si>
+  <si>
+    <t>Raúl ASENCIO</t>
+  </si>
+  <si>
+    <t>Morgan GIBBS-WHITE</t>
+  </si>
+  <si>
+    <t>André-Franck ZAMBO ANGUISSA</t>
+  </si>
+  <si>
+    <t>Gabriel CARVALHO TEIXEIRA</t>
+  </si>
+  <si>
+    <t>Mohamed-Ali CHO</t>
+  </si>
+  <si>
+    <t>João PALHINHA</t>
+  </si>
+  <si>
+    <t>Ko ITAKURA</t>
+  </si>
+  <si>
+    <t>Kieran TRIPPIER</t>
+  </si>
+  <si>
+    <t>Norberto BETUNCAL</t>
+  </si>
+  <si>
+    <t>CLUB BRUGGE</t>
+  </si>
+  <si>
+    <t>SPORTING LISBONA</t>
+  </si>
+  <si>
+    <t>Rômulo José CARDOSO DA CRUZ</t>
+  </si>
+  <si>
+    <t>Juan FOYTH</t>
+  </si>
+  <si>
+    <t>Rúben NEVES</t>
+  </si>
+  <si>
+    <t>CHELSEA</t>
+  </si>
+  <si>
+    <t>Franck KESSIÉ</t>
+  </si>
+  <si>
+    <t>Adrián BERNABÉ</t>
+  </si>
+  <si>
+    <t>PORTO</t>
+  </si>
+  <si>
+    <t>Brajan GRUDA</t>
+  </si>
+  <si>
+    <t>Controriscatto esercitato</t>
+  </si>
+  <si>
+    <t>Jarrod BOWEN</t>
+  </si>
+  <si>
+    <t>FIORENTINA</t>
+  </si>
+  <si>
+    <t>Matte SMETS</t>
+  </si>
+  <si>
+    <t>Noa LANG</t>
+  </si>
+  <si>
+    <t>Mika MÁRMOL</t>
+  </si>
+  <si>
+    <t>Julen AGIRREZABALA</t>
+  </si>
+  <si>
+    <t>Quim JUNYENT</t>
+  </si>
+  <si>
+    <t>George ILENIKHENA</t>
+  </si>
+  <si>
+    <t>Mattia LIBERALI</t>
+  </si>
+  <si>
+    <t>Sebastiano ESPOSITO</t>
+  </si>
+  <si>
+    <t>John STONES</t>
+  </si>
+  <si>
+    <t>Nathan TELLA</t>
+  </si>
+  <si>
+    <t>Tyrell MALACIA</t>
+  </si>
+  <si>
+    <t>Maxime ESTÈVE</t>
+  </si>
+  <si>
+    <t>Facundo BUONANOTTE</t>
+  </si>
+  <si>
+    <t>Mathias DELORGE</t>
+  </si>
+  <si>
+    <t>Antoine GRIEZMANN</t>
+  </si>
+  <si>
+    <t>Lucas LOPES BERALDO</t>
+  </si>
+  <si>
+    <t>Roméo LAVIA</t>
+  </si>
+  <si>
+    <t>Hákon Arnar HARALDSSON</t>
+  </si>
+  <si>
+    <t>Loïs OPENDA</t>
+  </si>
+  <si>
+    <t>Nathan PATTERSON</t>
+  </si>
+  <si>
+    <t>Mohamed DARAMY</t>
+  </si>
+  <si>
+    <t>Allan SAINT-MAXIMIN</t>
+  </si>
+  <si>
+    <t>José GAYÀ</t>
+  </si>
+  <si>
+    <t>BAYERN MONACO</t>
+  </si>
+  <si>
+    <t>Amir RRAHMANI</t>
+  </si>
+  <si>
+    <t>Ferland MENDY</t>
+  </si>
+  <si>
+    <t>Marcus Wendel VALLE DA SILVA</t>
+  </si>
+  <si>
+    <t>ROMA</t>
+  </si>
+  <si>
+    <t>Jordan TEZE</t>
+  </si>
+  <si>
+    <t>Paul NEBEL</t>
+  </si>
+  <si>
+    <t>Rayane BOUNIDA</t>
+  </si>
+  <si>
+    <t>Devyne RENSCH</t>
+  </si>
+  <si>
+    <t>Sven MIJNANS</t>
+  </si>
+  <si>
+    <t>Julien DURANVILLE</t>
+  </si>
+  <si>
+    <t>Dominic SOLANKE</t>
+  </si>
+  <si>
+    <t>LIONE</t>
+  </si>
+  <si>
+    <t>Aaron RAMSDALE</t>
+  </si>
+  <si>
+    <t>Ayase UEDA</t>
+  </si>
+  <si>
+    <t>Assane DIAO</t>
+  </si>
+  <si>
+    <t>Josh KING</t>
+  </si>
+  <si>
+    <t>Konrad LAIMER</t>
+  </si>
+  <si>
+    <t>Filippo MANÉ</t>
+  </si>
+  <si>
+    <t>José GIMÉNEZ</t>
+  </si>
+  <si>
+    <t>Eljif ELMAS</t>
+  </si>
+  <si>
+    <t>Yan DIOMANDÉ</t>
+  </si>
+  <si>
+    <t>Dani VIVIAN</t>
+  </si>
+  <si>
+    <t>Mohammed KUDUS</t>
+  </si>
+  <si>
+    <t>Liam DELAP</t>
+  </si>
+  <si>
+    <t>Robinio VAZ</t>
+  </si>
+  <si>
+    <t>SQUADRA</t>
+  </si>
+  <si>
+    <t>NOME
+UTENTE</t>
+  </si>
+  <si>
+    <t>ACCOUNT TELEGRAM</t>
+  </si>
+  <si>
+    <t>ACCOUNT FORUM</t>
+  </si>
+  <si>
+    <t>INGRESSO FMTO</t>
+  </si>
+  <si>
+    <t>ULTIMO CAMBIO CLUB</t>
+  </si>
+  <si>
+    <t>Alessandro</t>
+  </si>
+  <si>
+    <t>alessandromicciullo</t>
+  </si>
+  <si>
+    <t>ucavadd</t>
+  </si>
+  <si>
+    <t>ANDERLECHT</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>Fred994</t>
+  </si>
+  <si>
+    <t>Dieguito94</t>
+  </si>
+  <si>
+    <t>ARSENAL</t>
+  </si>
+  <si>
+    <t>alca_91</t>
+  </si>
+  <si>
+    <t>Alca91</t>
+  </si>
+  <si>
+    <t>Alex Casinghino</t>
+  </si>
+  <si>
+    <t>MrAlexDea</t>
+  </si>
+  <si>
+    <t>MrAlex</t>
+  </si>
+  <si>
+    <t>ATHLETIC BILBAO</t>
+  </si>
+  <si>
+    <t>Gabriele Righini</t>
+  </si>
+  <si>
+    <t>Be Positive</t>
+  </si>
+  <si>
+    <t>Stefano</t>
+  </si>
+  <si>
+    <t>SteYoshi</t>
+  </si>
+  <si>
+    <t>SteYoshizu</t>
+  </si>
+  <si>
+    <t>Loris</t>
+  </si>
+  <si>
+    <t>cestoris</t>
+  </si>
+  <si>
+    <t>Alexbusa</t>
+  </si>
+  <si>
+    <t>busakoss</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>SirDerfel</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>ivan19928</t>
+  </si>
+  <si>
+    <t>ivan16892</t>
+  </si>
+  <si>
+    <t>Paolo</t>
+  </si>
+  <si>
+    <t>paolo</t>
+  </si>
+  <si>
+    <t>Paolo_S77</t>
+  </si>
+  <si>
+    <t>BODO/GLIMT</t>
+  </si>
+  <si>
+    <t>Giuseppe Defilippis</t>
+  </si>
+  <si>
+    <t>gdef12</t>
+  </si>
+  <si>
+    <t>g.def12</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>Thefirstlady2025</t>
+  </si>
+  <si>
+    <t>Diemotions87</t>
+  </si>
+  <si>
+    <t>alerosati</t>
+  </si>
+  <si>
+    <t>alerosati2000</t>
+  </si>
+  <si>
+    <t>Carmeloct46</t>
+  </si>
+  <si>
+    <t>CELTIC</t>
+  </si>
+  <si>
+    <t>Luca</t>
+  </si>
+  <si>
+    <t>ferro197475</t>
+  </si>
+  <si>
+    <t>Ferro50</t>
+  </si>
+  <si>
+    <t>Fabrizio</t>
+  </si>
+  <si>
+    <t>Calonderiel</t>
+  </si>
+  <si>
+    <t>Roberto Sferruzzi</t>
+  </si>
+  <si>
+    <t>@sfero75</t>
+  </si>
+  <si>
+    <t>Sfero75</t>
+  </si>
+  <si>
+    <t>Giuliano</t>
+  </si>
+  <si>
+    <t>riccio76</t>
+  </si>
+  <si>
+    <t>giugiu49@</t>
+  </si>
+  <si>
+    <t>CRYSTAL PALACE</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>Andreav0105</t>
+  </si>
+  <si>
+    <t>DINAMO KIEV</t>
+  </si>
+  <si>
+    <t>L_Lawliet91</t>
+  </si>
+  <si>
+    <t>LucaLawliet</t>
+  </si>
+  <si>
+    <t>DINAMO ZAGABRIA</t>
+  </si>
+  <si>
+    <t>Lorenzo Galluzzo</t>
+  </si>
+  <si>
+    <t>galluzzolorenzo</t>
+  </si>
+  <si>
+    <t>Federico Luigelli</t>
+  </si>
+  <si>
+    <t>Gabriele Cavallaro</t>
+  </si>
+  <si>
+    <t>gabrieltheyellow</t>
+  </si>
+  <si>
+    <t>GENT</t>
+  </si>
+  <si>
+    <t>Alberto Ariatti</t>
+  </si>
+  <si>
+    <t>albertoariatti</t>
+  </si>
+  <si>
+    <t>Eurodino</t>
+  </si>
+  <si>
+    <t>Luca Marcarini</t>
+  </si>
+  <si>
+    <t>M17GK</t>
+  </si>
+  <si>
+    <t>Mec17</t>
+  </si>
+  <si>
+    <t>JUVENTUS</t>
+  </si>
+  <si>
+    <t>Asik85</t>
+  </si>
+  <si>
+    <t>Parzival1985</t>
+  </si>
+  <si>
+    <t>Tony My</t>
+  </si>
+  <si>
+    <t>tonetto87</t>
+  </si>
+  <si>
+    <t>Vin</t>
+  </si>
+  <si>
+    <t>vinci994</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>welshwizard07</t>
+  </si>
+  <si>
+    <t>Welsh wizard</t>
+  </si>
+  <si>
+    <t>Simone</t>
+  </si>
+  <si>
+    <t>@simo319797</t>
+  </si>
+  <si>
+    <t>Simogiunto97</t>
+  </si>
+  <si>
+    <t>whitewolf7432</t>
+  </si>
+  <si>
+    <t>Whitewolf7432</t>
+  </si>
+  <si>
+    <t>Alessandro Frangiosa</t>
+  </si>
+  <si>
+    <t>lisandro</t>
+  </si>
+  <si>
+    <t>Alefra88</t>
+  </si>
+  <si>
+    <t>Michele Martinelli</t>
+  </si>
+  <si>
+    <t>@Mikkael90</t>
+  </si>
+  <si>
+    <t>mikkael90</t>
+  </si>
+  <si>
+    <t>Marco Jack Nanni</t>
+  </si>
+  <si>
+    <t>Marcojacknanni</t>
+  </si>
+  <si>
+    <t>jackdicuori5</t>
+  </si>
+  <si>
+    <t>Vittorio Vaglia</t>
+  </si>
+  <si>
+    <t>Vjr75</t>
+  </si>
+  <si>
+    <t>NEWCASTLE</t>
+  </si>
+  <si>
+    <t>Antonio Senserini</t>
+  </si>
+  <si>
+    <t>piesal</t>
+  </si>
+  <si>
+    <t>piesal09</t>
+  </si>
+  <si>
+    <t>Fabio Pierotti</t>
+  </si>
+  <si>
+    <t>PAOK SALONICCO</t>
+  </si>
+  <si>
+    <t>Michele Sivilli</t>
+  </si>
+  <si>
+    <t>Michelone74</t>
+  </si>
+  <si>
+    <t>Michelone 74</t>
+  </si>
+  <si>
+    <t>Tommaso Molin</t>
+  </si>
+  <si>
+    <t>tommy150788</t>
+  </si>
+  <si>
+    <t>Tommy_8888</t>
+  </si>
+  <si>
+    <t>Giulio Mercurio</t>
+  </si>
+  <si>
+    <t>fufo8</t>
+  </si>
+  <si>
+    <t>jmerk1702</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>@AgasiZ</t>
+  </si>
+  <si>
+    <t>Agasiz</t>
+  </si>
+  <si>
+    <t>Luigi Formisano</t>
+  </si>
+  <si>
+    <t>folu92</t>
+  </si>
+  <si>
+    <t>REAL MADRID</t>
+  </si>
+  <si>
+    <t>marco barilla'</t>
+  </si>
+  <si>
+    <t>mandraghe76</t>
+  </si>
+  <si>
+    <t>mandraghe76@</t>
+  </si>
+  <si>
+    <t>REAL SOCIEDAD</t>
+  </si>
+  <si>
+    <t>Tocci Raffaele</t>
+  </si>
+  <si>
+    <t>ciaffa69</t>
+  </si>
+  <si>
+    <t>prinz691</t>
+  </si>
+  <si>
+    <t>Manu Nyhr Gdr</t>
+  </si>
+  <si>
+    <t>NyhrGdr</t>
+  </si>
+  <si>
+    <t>NyhrGaming</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>RoyFox83</t>
+  </si>
+  <si>
+    <t>SIVIGLIA</t>
+  </si>
+  <si>
+    <t>Lvcaalexis</t>
+  </si>
+  <si>
+    <t>lvcaalexis</t>
+  </si>
+  <si>
+    <t>Nando</t>
+  </si>
+  <si>
+    <t>Hones80</t>
+  </si>
+  <si>
+    <t>Hones80s</t>
+  </si>
+  <si>
+    <t>Luigi valentino</t>
+  </si>
+  <si>
+    <t>Giggio</t>
+  </si>
+  <si>
+    <t>giggio</t>
+  </si>
+  <si>
+    <t>TOTTENHAM</t>
+  </si>
+  <si>
+    <t>Osvaldo</t>
+  </si>
+  <si>
+    <t>Osvaldo13</t>
+  </si>
+  <si>
+    <t>osv98</t>
+  </si>
+  <si>
+    <t>Alberto Giglio</t>
+  </si>
+  <si>
+    <t>albertogiglio</t>
+  </si>
+  <si>
+    <t>giglioa386</t>
+  </si>
+  <si>
+    <t>VILLARREAL</t>
+  </si>
+  <si>
+    <t>Fabio Ceol</t>
+  </si>
+  <si>
+    <t>fabkey</t>
+  </si>
+  <si>
+    <t>FCL</t>
+  </si>
+  <si>
+    <t>Antonio Greggio</t>
+  </si>
+  <si>
+    <t>TonioTaras</t>
+  </si>
+  <si>
+    <t>Tommy WATSON</t>
+  </si>
+  <si>
+    <t>Claudio ECHEVERRI</t>
+  </si>
+  <si>
+    <t>Yann SOMMER</t>
+  </si>
+  <si>
+    <t>Robin LE NORMAND</t>
+  </si>
+  <si>
+    <t>Francisco TRINCÃO</t>
+  </si>
+  <si>
+    <t>Bernardo SILVA</t>
+  </si>
+  <si>
+    <t>Romelu LUKAKU</t>
+  </si>
+  <si>
+    <t>Stefano TURATI</t>
+  </si>
+  <si>
+    <t>Tommaso POBEGA</t>
+  </si>
+  <si>
+    <t>Marten DE ROON</t>
+  </si>
+  <si>
+    <t>Josip ŠUTALO</t>
+  </si>
+  <si>
+    <t>Noah SADIKI</t>
+  </si>
+  <si>
+    <t>Petar SUČIĆ</t>
+  </si>
+  <si>
+    <t>Romano SCHMID</t>
+  </si>
+  <si>
+    <t>Prestito con diritto di riscatto</t>
+  </si>
+  <si>
+    <t>Mamadou SARR</t>
+  </si>
+  <si>
+    <t>Prestito con controriscatto</t>
+  </si>
+  <si>
+    <t>Atakan KARAZOR</t>
+  </si>
+  <si>
+    <t>Luís Henrique TOMAZ DE LIMA</t>
+  </si>
+  <si>
+    <t>Jonathan TAH</t>
+  </si>
+  <si>
+    <t>Natan Bernardo DE SOUZA</t>
+  </si>
+  <si>
+    <t>Benjamin WHITE</t>
+  </si>
+  <si>
+    <t>Joe GOMEZ</t>
+  </si>
+  <si>
+    <t>Christian NØRGAARD</t>
+  </si>
+  <si>
+    <t>Caleb WILEY</t>
+  </si>
+  <si>
+    <t>Arthur ATTA</t>
+  </si>
+  <si>
+    <t>Paulo DYBALA</t>
+  </si>
+  <si>
+    <t>Matt O'RILEY</t>
+  </si>
+  <si>
+    <t>Youri TIELEMANS</t>
+  </si>
+  <si>
+    <t>Nick WOLTEMADE</t>
+  </si>
+  <si>
+    <t>Brooke NORTON-CUFFY</t>
+  </si>
+  <si>
+    <t>Lesley UGOCHUKWU</t>
+  </si>
+  <si>
+    <t>Jonathan DAVID</t>
+  </si>
+  <si>
+    <t>Jonas URBIG</t>
+  </si>
+  <si>
+    <t>Rinuncia recompra o diritto di riacquisto</t>
+  </si>
+  <si>
+    <t>Obed NKAMBADIO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -389,8 +1320,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -724,8 +1656,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6F8EC8-570C-45A6-A3F9-20FAD10EBF7E}">
-  <dimension ref="A1:F70"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
@@ -734,9 +1666,10 @@
     <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -747,1340 +1680,5774 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>91108805</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>45104608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>67283140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>98040226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>43591641</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>78088646</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="E8">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>96102946</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>43094553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>49048348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>28121369</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>28106684</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>57178516</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G14">
+        <v>2000108364</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G15">
+        <v>29219115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G16">
+        <v>14229525</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <v>91205203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G18">
+        <v>28103590</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>83209468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>49062287</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G21">
+        <v>49034219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G22">
+        <v>43167354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G23">
+        <v>16254093</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="G24">
+        <v>2000091517</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>37060600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G26">
+        <v>28127875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E27">
         <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G27">
+        <v>14048343</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G28">
+        <v>67011248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>2000168014</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30">
+        <v>2000168014</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G31">
+        <v>2000402904</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G32">
+        <v>43298002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G33">
+        <v>19383257</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G34">
+        <v>24048100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G35">
+        <v>16202373</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G36">
+        <v>2000097929</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E37">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>76063258</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C38" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="E38">
         <v>30</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38">
+        <v>76063258</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39">
+        <v>49048469</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
         <v>59</v>
       </c>
-      <c r="D39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" t="s">
-        <v>49</v>
-      </c>
       <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40">
+        <v>2000178883</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="s">
         <v>59</v>
       </c>
-      <c r="D40" t="s">
-        <v>98</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41">
+        <v>2000426277</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" t="s">
         <v>59</v>
       </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" t="s">
-        <v>49</v>
-      </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G42">
+        <v>37024733</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G43">
+        <v>43429372</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G44">
+        <v>83169817</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G45">
+        <v>29216094</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G46">
+        <v>95078288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G47">
+        <v>80034923</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G48">
+        <v>67276482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" t="s">
         <v>69</v>
       </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
       <c r="C49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E49">
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G49">
+        <v>91188349</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50">
+        <v>19377206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" t="s">
         <v>59</v>
       </c>
-      <c r="C50" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" t="s">
-        <v>98</v>
-      </c>
-      <c r="E50">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" t="s">
-        <v>49</v>
-      </c>
       <c r="C51" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E51">
         <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G51">
+        <v>85078880</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E52">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G52">
+        <v>98029385</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G53">
+        <v>43500245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G54">
+        <v>85145172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E55">
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="G55">
+        <v>18108550</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>89</v>
+      </c>
+      <c r="G56">
+        <v>2000107424</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57">
+        <v>48044499</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58">
+        <v>51067947</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59">
+        <v>85104424</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60">
+        <v>62096282</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61">
+        <v>67260440</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>93</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62">
+        <v>43500350</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" t="s">
         <v>59</v>
       </c>
-      <c r="D56" t="s">
-        <v>105</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>79</v>
-      </c>
-      <c r="B57" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C63" t="s">
         <v>98</v>
       </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63">
+        <v>37024470</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64">
+        <v>12088462</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>80</v>
-      </c>
-      <c r="B58" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
-        <v>98</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" t="s">
-        <v>82</v>
-      </c>
-      <c r="C60" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" t="s">
-        <v>4</v>
-      </c>
-      <c r="C61" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62" t="s">
-        <v>4</v>
-      </c>
-      <c r="C62" t="s">
-        <v>82</v>
-      </c>
-      <c r="D62" t="s">
-        <v>98</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>86</v>
-      </c>
-      <c r="B63" t="s">
-        <v>49</v>
-      </c>
-      <c r="C63" t="s">
-        <v>87</v>
-      </c>
-      <c r="D63" t="s">
-        <v>98</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>88</v>
-      </c>
-      <c r="B64" t="s">
-        <v>87</v>
-      </c>
-      <c r="C64" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64" t="s">
-        <v>98</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>89</v>
-      </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G65">
+        <v>37026994</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E66">
         <v>2</v>
       </c>
       <c r="F66" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66">
+        <v>76014012</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>91</v>
-      </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E67">
         <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G67">
+        <v>83335576</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D68" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E68">
         <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G68">
+        <v>2000191507</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D69" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E69">
         <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G69">
+        <v>2000054475</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E70">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>102</v>
+        <v>28</v>
+      </c>
+      <c r="G70">
+        <v>59006269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71">
+        <v>92065436</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>84</v>
+      </c>
+      <c r="D72" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72">
+        <v>2000014205</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73">
+        <v>2000221458</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>109</v>
+      </c>
+      <c r="B74" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74">
+        <v>37070210</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75">
+        <v>29233148</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76">
+        <v>2000288856</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>114</v>
+      </c>
+      <c r="B77" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77">
+        <v>78076343</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>115</v>
+      </c>
+      <c r="B78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C78" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78">
+        <v>16191724</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C79" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79">
+        <v>2000258392</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>117</v>
+      </c>
+      <c r="B80" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80">
+        <v>49038967</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81">
+        <v>2000186151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>119</v>
+      </c>
+      <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82">
+        <v>2000330855</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83">
+        <v>12091814</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84">
+        <v>92023410</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>122</v>
+      </c>
+      <c r="B85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" t="s">
+        <v>31</v>
+      </c>
+      <c r="D85" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85">
+        <v>85111795</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86">
+        <v>76033272</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>125</v>
+      </c>
+      <c r="B87" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87">
+        <v>4</v>
+      </c>
+      <c r="F87" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87">
+        <v>2000039995</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" t="s">
+        <v>59</v>
+      </c>
+      <c r="C88" t="s">
+        <v>127</v>
+      </c>
+      <c r="D88" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88">
+        <v>6</v>
+      </c>
+      <c r="F88" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88">
+        <v>67201634</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" t="s">
+        <v>50</v>
+      </c>
+      <c r="D89" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89">
+        <v>2000146948</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>129</v>
+      </c>
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90">
+        <v>2000124287</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>130</v>
+      </c>
+      <c r="B91" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" t="s">
+        <v>50</v>
+      </c>
+      <c r="D91" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91">
+        <v>2000311463</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>131</v>
+      </c>
+      <c r="B92" t="s">
+        <v>50</v>
+      </c>
+      <c r="C92" t="s">
+        <v>67</v>
+      </c>
+      <c r="D92" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92">
+        <v>7</v>
+      </c>
+      <c r="F92" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92">
+        <v>2000125958</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>132</v>
+      </c>
+      <c r="B93" t="s">
+        <v>59</v>
+      </c>
+      <c r="C93" t="s">
+        <v>84</v>
+      </c>
+      <c r="D93" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93">
+        <v>2000188768</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>133</v>
+      </c>
+      <c r="B94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C94" t="s">
+        <v>59</v>
+      </c>
+      <c r="D94" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94">
+        <v>2000098016</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>134</v>
+      </c>
+      <c r="B95" t="s">
+        <v>38</v>
+      </c>
+      <c r="C95" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95">
+        <v>15</v>
+      </c>
+      <c r="F95" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95">
+        <v>2000104173</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96">
+        <v>91151058</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>137</v>
+      </c>
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" t="s">
+        <v>136</v>
+      </c>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97">
+        <v>29186418</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>138</v>
+      </c>
+      <c r="B98" t="s">
+        <v>69</v>
+      </c>
+      <c r="C98" t="s">
+        <v>98</v>
+      </c>
+      <c r="D98" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98">
+        <v>91206105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99" t="s">
+        <v>98</v>
+      </c>
+      <c r="C99" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99">
+        <v>37076141</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>140</v>
+      </c>
+      <c r="B100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" t="s">
+        <v>84</v>
+      </c>
+      <c r="D100" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100">
+        <v>37060922</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>141</v>
+      </c>
+      <c r="B101" t="s">
+        <v>84</v>
+      </c>
+      <c r="C101" t="s">
+        <v>38</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101">
+        <v>91138280</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>142</v>
+      </c>
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" t="s">
+        <v>89</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" t="s">
+        <v>89</v>
+      </c>
+      <c r="G102">
+        <v>64016316</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>143</v>
+      </c>
+      <c r="B103" t="s">
+        <v>39</v>
+      </c>
+      <c r="C103" t="s">
+        <v>26</v>
+      </c>
+      <c r="D103" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103">
+        <v>71081391</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>144</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104">
+        <v>19171604</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>39</v>
+      </c>
+      <c r="D105" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105">
+        <v>14000219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>146</v>
+      </c>
+      <c r="B106" t="s">
+        <v>147</v>
+      </c>
+      <c r="C106" t="s">
+        <v>50</v>
+      </c>
+      <c r="D106" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106">
+        <v>86080170</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>148</v>
+      </c>
+      <c r="B107" t="s">
+        <v>147</v>
+      </c>
+      <c r="C107" t="s">
+        <v>50</v>
+      </c>
+      <c r="D107" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107">
+        <v>2000058198</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>149</v>
+      </c>
+      <c r="B108" t="s">
+        <v>50</v>
+      </c>
+      <c r="C108" t="s">
+        <v>147</v>
+      </c>
+      <c r="D108" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108">
+        <v>2000020287</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>150</v>
+      </c>
+      <c r="B109" t="s">
+        <v>147</v>
+      </c>
+      <c r="C109" t="s">
+        <v>151</v>
+      </c>
+      <c r="D109" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" t="s">
+        <v>22</v>
+      </c>
+      <c r="G109">
+        <v>2000120742</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>152</v>
+      </c>
+      <c r="B110" t="s">
+        <v>151</v>
+      </c>
+      <c r="C110" t="s">
+        <v>147</v>
+      </c>
+      <c r="D110" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110">
+        <v>28126249</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" t="s">
+        <v>88</v>
+      </c>
+      <c r="C111" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111">
+        <v>19233491</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>154</v>
+      </c>
+      <c r="B112" t="s">
+        <v>69</v>
+      </c>
+      <c r="C112" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112">
+        <v>15</v>
+      </c>
+      <c r="F112" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112">
+        <v>2000126407</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>155</v>
+      </c>
+      <c r="B113" t="s">
+        <v>69</v>
+      </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113">
+        <v>29175220</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>156</v>
+      </c>
+      <c r="B114" t="s">
+        <v>112</v>
+      </c>
+      <c r="C114" t="s">
+        <v>69</v>
+      </c>
+      <c r="D114" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114">
+        <v>48030711</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>157</v>
+      </c>
+      <c r="B115" t="s">
+        <v>112</v>
+      </c>
+      <c r="C115" t="s">
+        <v>69</v>
+      </c>
+      <c r="D115" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115" t="s">
+        <v>22</v>
+      </c>
+      <c r="G115">
+        <v>2000273988</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>158</v>
+      </c>
+      <c r="B116" t="s">
+        <v>136</v>
+      </c>
+      <c r="C116" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116">
+        <v>2000006280</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>159</v>
+      </c>
+      <c r="B117" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" t="s">
+        <v>136</v>
+      </c>
+      <c r="D117" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117">
+        <v>6</v>
+      </c>
+      <c r="F117" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117">
+        <v>55070285</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>160</v>
+      </c>
+      <c r="B118" t="s">
+        <v>112</v>
+      </c>
+      <c r="C118" t="s">
+        <v>127</v>
+      </c>
+      <c r="D118" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118">
+        <v>5</v>
+      </c>
+      <c r="F118" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118">
+        <v>45092658</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>161</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
+        <v>20</v>
+      </c>
+      <c r="D119" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119">
+        <v>28018613</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>162</v>
+      </c>
+      <c r="B120" t="s">
+        <v>163</v>
+      </c>
+      <c r="C120" t="s">
+        <v>164</v>
+      </c>
+      <c r="D120" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120">
+        <v>83228124</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>165</v>
+      </c>
+      <c r="B121" t="s">
+        <v>164</v>
+      </c>
+      <c r="C121" t="s">
+        <v>163</v>
+      </c>
+      <c r="D121" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121">
+        <v>10</v>
+      </c>
+      <c r="F121" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121">
+        <v>19380090</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>166</v>
+      </c>
+      <c r="B122" t="s">
+        <v>163</v>
+      </c>
+      <c r="C122" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122">
+        <v>15</v>
+      </c>
+      <c r="F122" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122">
+        <v>14186894</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>167</v>
+      </c>
+      <c r="B123" t="s">
+        <v>168</v>
+      </c>
+      <c r="C123" t="s">
+        <v>84</v>
+      </c>
+      <c r="D123" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123">
+        <v>4</v>
+      </c>
+      <c r="F123" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123">
+        <v>55070307</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>169</v>
+      </c>
+      <c r="B124" t="s">
+        <v>84</v>
+      </c>
+      <c r="C124" t="s">
+        <v>168</v>
+      </c>
+      <c r="D124" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124">
+        <v>13136664</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>170</v>
+      </c>
+      <c r="B125" t="s">
+        <v>84</v>
+      </c>
+      <c r="C125" t="s">
+        <v>171</v>
+      </c>
+      <c r="D125" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125">
+        <v>14</v>
+      </c>
+      <c r="F125" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125">
+        <v>67271025</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>172</v>
+      </c>
+      <c r="B126" t="s">
+        <v>88</v>
+      </c>
+      <c r="C126" t="s">
+        <v>69</v>
+      </c>
+      <c r="D126" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126">
+        <v>2000180822</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>172</v>
+      </c>
+      <c r="B127" t="s">
+        <v>69</v>
+      </c>
+      <c r="C127" t="s">
+        <v>88</v>
+      </c>
+      <c r="D127" t="s">
+        <v>173</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>173</v>
+      </c>
+      <c r="G127">
+        <v>2000180822</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>174</v>
+      </c>
+      <c r="B128" t="s">
+        <v>175</v>
+      </c>
+      <c r="C128" t="s">
+        <v>98</v>
+      </c>
+      <c r="D128" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128">
+        <v>29125842</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>176</v>
+      </c>
+      <c r="B129" t="s">
+        <v>98</v>
+      </c>
+      <c r="C129" t="s">
+        <v>175</v>
+      </c>
+      <c r="D129" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129" t="s">
+        <v>22</v>
+      </c>
+      <c r="G129">
+        <v>2000062325</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>177</v>
+      </c>
+      <c r="B130" t="s">
+        <v>98</v>
+      </c>
+      <c r="C130" t="s">
+        <v>175</v>
+      </c>
+      <c r="D130" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130">
+        <v>37055842</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>178</v>
+      </c>
+      <c r="B131" t="s">
+        <v>69</v>
+      </c>
+      <c r="C131" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131">
+        <v>11</v>
+      </c>
+      <c r="F131" t="s">
+        <v>28</v>
+      </c>
+      <c r="G131">
+        <v>67295761</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>179</v>
+      </c>
+      <c r="B132" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132">
+        <v>11</v>
+      </c>
+      <c r="F132" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132">
+        <v>67277830</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>180</v>
+      </c>
+      <c r="B133" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" t="s">
+        <v>46</v>
+      </c>
+      <c r="D133" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133" t="s">
+        <v>22</v>
+      </c>
+      <c r="G133">
+        <v>2000297440</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>181</v>
+      </c>
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" t="s">
+        <v>46</v>
+      </c>
+      <c r="D134" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134" t="s">
+        <v>22</v>
+      </c>
+      <c r="G134">
+        <v>2000214136</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>182</v>
+      </c>
+      <c r="B135" t="s">
+        <v>46</v>
+      </c>
+      <c r="C135" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135">
+        <v>5</v>
+      </c>
+      <c r="F135" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135">
+        <v>2000252799</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>183</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" t="s">
+        <v>10</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136">
+        <v>43425069</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>184</v>
+      </c>
+      <c r="B137" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" t="s">
+        <v>16</v>
+      </c>
+      <c r="D137" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137">
+        <v>20</v>
+      </c>
+      <c r="F137" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137">
+        <v>28060397</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>185</v>
+      </c>
+      <c r="B138" t="s">
+        <v>136</v>
+      </c>
+      <c r="C138" t="s">
+        <v>164</v>
+      </c>
+      <c r="D138" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138">
+        <v>8</v>
+      </c>
+      <c r="F138" t="s">
+        <v>28</v>
+      </c>
+      <c r="G138">
+        <v>28106683</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>186</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" t="s">
+        <v>124</v>
+      </c>
+      <c r="D139" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="F139" t="s">
+        <v>28</v>
+      </c>
+      <c r="G139">
+        <v>37058363</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>187</v>
+      </c>
+      <c r="B140" t="s">
+        <v>39</v>
+      </c>
+      <c r="C140" t="s">
+        <v>93</v>
+      </c>
+      <c r="D140" t="s">
+        <v>10</v>
+      </c>
+      <c r="E140">
+        <v>5</v>
+      </c>
+      <c r="F140" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140">
+        <v>49060933</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>188</v>
+      </c>
+      <c r="B141" t="s">
+        <v>93</v>
+      </c>
+      <c r="C141" t="s">
+        <v>39</v>
+      </c>
+      <c r="D141" t="s">
+        <v>10</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141">
+        <v>2000051578</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>189</v>
+      </c>
+      <c r="B142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" t="s">
+        <v>10</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142">
+        <v>2000022218</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>49</v>
+      </c>
+      <c r="B143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143">
+        <v>2000091517</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>190</v>
+      </c>
+      <c r="B144" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144">
+        <v>5</v>
+      </c>
+      <c r="F144" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144">
+        <v>67086656</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>191</v>
+      </c>
+      <c r="B145" t="s">
+        <v>50</v>
+      </c>
+      <c r="C145" t="s">
+        <v>53</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145">
+        <v>2000094252</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>192</v>
+      </c>
+      <c r="B146" t="s">
+        <v>50</v>
+      </c>
+      <c r="C146" t="s">
+        <v>53</v>
+      </c>
+      <c r="D146" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146">
+        <v>18115012</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>193</v>
+      </c>
+      <c r="B147" t="s">
+        <v>53</v>
+      </c>
+      <c r="C147" t="s">
+        <v>50</v>
+      </c>
+      <c r="D147" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147">
+        <v>39060464</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>194</v>
+      </c>
+      <c r="B148" t="s">
+        <v>53</v>
+      </c>
+      <c r="C148" t="s">
+        <v>50</v>
+      </c>
+      <c r="D148" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148">
+        <v>18101745</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>195</v>
+      </c>
+      <c r="B149" t="s">
+        <v>21</v>
+      </c>
+      <c r="C149" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+      <c r="F149" t="s">
+        <v>22</v>
+      </c>
+      <c r="G149">
+        <v>61083649</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>196</v>
+      </c>
+      <c r="B150" t="s">
+        <v>21</v>
+      </c>
+      <c r="C150" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+      <c r="F150" t="s">
+        <v>22</v>
+      </c>
+      <c r="G150">
+        <v>27148020</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>197</v>
+      </c>
+      <c r="B151" t="s">
+        <v>8</v>
+      </c>
+      <c r="C151" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="F151" t="s">
+        <v>22</v>
+      </c>
+      <c r="G151">
+        <v>85132406</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>198</v>
+      </c>
+      <c r="B152" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" t="s">
+        <v>199</v>
+      </c>
+      <c r="D152" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152">
+        <v>67178177</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>200</v>
+      </c>
+      <c r="B153" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" t="s">
+        <v>199</v>
+      </c>
+      <c r="D153" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153" t="s">
+        <v>22</v>
+      </c>
+      <c r="G153">
+        <v>11023165</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>201</v>
+      </c>
+      <c r="B154" t="s">
+        <v>199</v>
+      </c>
+      <c r="C154" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154" t="s">
+        <v>22</v>
+      </c>
+      <c r="G154">
+        <v>85133751</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>202</v>
+      </c>
+      <c r="B155" t="s">
+        <v>203</v>
+      </c>
+      <c r="C155" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155">
+        <v>6</v>
+      </c>
+      <c r="F155" t="s">
+        <v>28</v>
+      </c>
+      <c r="G155">
+        <v>90072860</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>204</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" t="s">
+        <v>98</v>
+      </c>
+      <c r="D156" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156">
+        <v>37058008</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>205</v>
+      </c>
+      <c r="B157" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" t="s">
+        <v>98</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157">
+        <v>91188358</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>206</v>
+      </c>
+      <c r="B158" t="s">
+        <v>18</v>
+      </c>
+      <c r="C158" t="s">
+        <v>98</v>
+      </c>
+      <c r="D158" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158">
+        <v>2000127879</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>207</v>
+      </c>
+      <c r="B159" t="s">
+        <v>98</v>
+      </c>
+      <c r="C159" t="s">
+        <v>18</v>
+      </c>
+      <c r="D159" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+      <c r="F159" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159">
+        <v>37073313</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>208</v>
+      </c>
+      <c r="B160" t="s">
+        <v>98</v>
+      </c>
+      <c r="C160" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160" t="s">
+        <v>22</v>
+      </c>
+      <c r="G160">
+        <v>37077008</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>209</v>
+      </c>
+      <c r="B161" t="s">
+        <v>98</v>
+      </c>
+      <c r="C161" t="s">
+        <v>18</v>
+      </c>
+      <c r="D161" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="F161" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161">
+        <v>2000155483</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>210</v>
+      </c>
+      <c r="B162" t="s">
+        <v>21</v>
+      </c>
+      <c r="C162" t="s">
+        <v>211</v>
+      </c>
+      <c r="D162" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162" t="s">
+        <v>22</v>
+      </c>
+      <c r="G162">
+        <v>29125191</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>212</v>
+      </c>
+      <c r="B163" t="s">
+        <v>211</v>
+      </c>
+      <c r="C163" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" t="s">
+        <v>10</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163">
+        <v>29137172</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>213</v>
+      </c>
+      <c r="B164" t="s">
+        <v>211</v>
+      </c>
+      <c r="C164" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+      <c r="F164" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164">
+        <v>45111868</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>214</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="s">
+        <v>211</v>
+      </c>
+      <c r="D165" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165">
+        <v>55</v>
+      </c>
+      <c r="F165" t="s">
+        <v>28</v>
+      </c>
+      <c r="G165">
+        <v>2000210791</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>215</v>
+      </c>
+      <c r="B166" t="s">
+        <v>147</v>
+      </c>
+      <c r="C166" t="s">
+        <v>93</v>
+      </c>
+      <c r="D166" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166">
+        <v>8</v>
+      </c>
+      <c r="F166" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166">
+        <v>2000276594</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>216</v>
+      </c>
+      <c r="B167" t="s">
+        <v>93</v>
+      </c>
+      <c r="C167" t="s">
+        <v>147</v>
+      </c>
+      <c r="D167" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167">
+        <v>16147659</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>217</v>
+      </c>
+      <c r="B168" t="s">
+        <v>147</v>
+      </c>
+      <c r="C168" t="s">
+        <v>16</v>
+      </c>
+      <c r="D168" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168">
+        <v>2000121585</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>218</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="s">
+        <v>147</v>
+      </c>
+      <c r="D169" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169">
+        <v>3</v>
+      </c>
+      <c r="F169" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169">
+        <v>78060464</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>219</v>
+      </c>
+      <c r="B170" t="s">
+        <v>93</v>
+      </c>
+      <c r="C170" t="s">
+        <v>211</v>
+      </c>
+      <c r="D170" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170">
+        <v>5</v>
+      </c>
+      <c r="F170" t="s">
+        <v>28</v>
+      </c>
+      <c r="G170">
+        <v>47064795</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>220</v>
+      </c>
+      <c r="B171" t="s">
+        <v>164</v>
+      </c>
+      <c r="C171" t="s">
+        <v>136</v>
+      </c>
+      <c r="D171" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171">
+        <v>2000311833</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>221</v>
+      </c>
+      <c r="B172" t="s">
+        <v>136</v>
+      </c>
+      <c r="C172" t="s">
+        <v>164</v>
+      </c>
+      <c r="D172" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+      <c r="F172" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172">
+        <v>67256618</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>222</v>
+      </c>
+      <c r="B173" t="s">
+        <v>136</v>
+      </c>
+      <c r="C173" t="s">
+        <v>164</v>
+      </c>
+      <c r="D173" t="s">
+        <v>10</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173">
+        <v>13200568</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>223</v>
+      </c>
+      <c r="B174" t="s">
+        <v>136</v>
+      </c>
+      <c r="C174" t="s">
+        <v>164</v>
+      </c>
+      <c r="D174" t="s">
+        <v>10</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174">
+        <v>28126247</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>224</v>
+      </c>
+      <c r="B175" t="s">
+        <v>136</v>
+      </c>
+      <c r="C175" t="s">
+        <v>164</v>
+      </c>
+      <c r="D175" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175">
+        <v>2000290881</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>384</v>
+      </c>
+      <c r="B176" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" t="s">
+        <v>67</v>
+      </c>
+      <c r="D176" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176">
+        <v>12</v>
+      </c>
+      <c r="F176" t="s">
+        <v>28</v>
+      </c>
+      <c r="G176">
+        <v>2000187717</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>385</v>
+      </c>
+      <c r="B177" t="s">
+        <v>8</v>
+      </c>
+      <c r="C177" t="s">
+        <v>50</v>
+      </c>
+      <c r="D177" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177">
+        <v>20</v>
+      </c>
+      <c r="F177" t="s">
+        <v>28</v>
+      </c>
+      <c r="G177">
+        <v>2000094152</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" t="s">
+        <v>127</v>
+      </c>
+      <c r="C178" t="s">
+        <v>39</v>
+      </c>
+      <c r="D178" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178">
+        <v>3</v>
+      </c>
+      <c r="F178" t="s">
+        <v>28</v>
+      </c>
+      <c r="G178">
+        <v>69000199</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>387</v>
+      </c>
+      <c r="B179" t="s">
+        <v>39</v>
+      </c>
+      <c r="C179" t="s">
+        <v>362</v>
+      </c>
+      <c r="D179" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179">
+        <v>22</v>
+      </c>
+      <c r="F179" t="s">
+        <v>28</v>
+      </c>
+      <c r="G179">
+        <v>48037162</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" t="s">
+        <v>303</v>
+      </c>
+      <c r="C180" t="s">
+        <v>112</v>
+      </c>
+      <c r="D180" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180">
+        <v>83137935</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>389</v>
+      </c>
+      <c r="B181" t="s">
+        <v>112</v>
+      </c>
+      <c r="C181" t="s">
+        <v>303</v>
+      </c>
+      <c r="D181" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181">
+        <v>55041632</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>390</v>
+      </c>
+      <c r="B182" t="s">
+        <v>112</v>
+      </c>
+      <c r="C182" t="s">
+        <v>303</v>
+      </c>
+      <c r="D182" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182">
+        <v>25</v>
+      </c>
+      <c r="F182" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182">
+        <v>18007344</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>391</v>
+      </c>
+      <c r="B183" t="s">
+        <v>84</v>
+      </c>
+      <c r="C183" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183" t="s">
+        <v>22</v>
+      </c>
+      <c r="G183">
+        <v>43378804</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>392</v>
+      </c>
+      <c r="B184" t="s">
+        <v>8</v>
+      </c>
+      <c r="C184" t="s">
+        <v>84</v>
+      </c>
+      <c r="D184" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184" t="s">
+        <v>22</v>
+      </c>
+      <c r="G184">
+        <v>43269242</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>393</v>
+      </c>
+      <c r="B185" t="s">
+        <v>378</v>
+      </c>
+      <c r="C185" t="s">
+        <v>362</v>
+      </c>
+      <c r="D185" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185">
+        <v>2</v>
+      </c>
+      <c r="F185" t="s">
+        <v>28</v>
+      </c>
+      <c r="G185">
+        <v>37001813</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>394</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="s">
+        <v>287</v>
+      </c>
+      <c r="D186" t="s">
+        <v>10</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186" t="s">
+        <v>28</v>
+      </c>
+      <c r="G186">
+        <v>24058106</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>395</v>
+      </c>
+      <c r="B187" t="s">
+        <v>38</v>
+      </c>
+      <c r="C187" t="s">
+        <v>290</v>
+      </c>
+      <c r="D187" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187">
+        <v>2000045005</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>395</v>
+      </c>
+      <c r="B188" t="s">
+        <v>290</v>
+      </c>
+      <c r="C188" t="s">
+        <v>38</v>
+      </c>
+      <c r="D188" t="s">
+        <v>173</v>
+      </c>
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188" t="s">
+        <v>173</v>
+      </c>
+      <c r="G188">
+        <v>2000045005</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>396</v>
+      </c>
+      <c r="B189" t="s">
+        <v>290</v>
+      </c>
+      <c r="C189" t="s">
+        <v>26</v>
+      </c>
+      <c r="D189" t="s">
+        <v>10</v>
+      </c>
+      <c r="E189">
+        <v>5</v>
+      </c>
+      <c r="F189" t="s">
+        <v>27</v>
+      </c>
+      <c r="G189">
+        <v>2000162930</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>397</v>
+      </c>
+      <c r="B190" t="s">
+        <v>88</v>
+      </c>
+      <c r="C190" t="s">
+        <v>69</v>
+      </c>
+      <c r="D190" t="s">
+        <v>398</v>
+      </c>
+      <c r="E190">
+        <v>2</v>
+      </c>
+      <c r="F190" t="s">
+        <v>398</v>
+      </c>
+      <c r="G190">
+        <v>16184737</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>399</v>
+      </c>
+      <c r="B191" t="s">
+        <v>88</v>
+      </c>
+      <c r="C191" t="s">
+        <v>69</v>
+      </c>
+      <c r="D191" t="s">
+        <v>400</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+      <c r="F191" t="s">
+        <v>400</v>
+      </c>
+      <c r="G191">
+        <v>2000107103</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>401</v>
+      </c>
+      <c r="B192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C192" t="s">
+        <v>378</v>
+      </c>
+      <c r="D192" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192">
+        <v>4</v>
+      </c>
+      <c r="F192" t="s">
+        <v>28</v>
+      </c>
+      <c r="G192">
+        <v>92074021</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>402</v>
+      </c>
+      <c r="B193" t="s">
+        <v>45</v>
+      </c>
+      <c r="C193" t="s">
+        <v>378</v>
+      </c>
+      <c r="D193" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193">
+        <v>15</v>
+      </c>
+      <c r="F193" t="s">
+        <v>28</v>
+      </c>
+      <c r="G193">
+        <v>19403484</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>403</v>
+      </c>
+      <c r="B194" t="s">
+        <v>147</v>
+      </c>
+      <c r="C194" t="s">
+        <v>20</v>
+      </c>
+      <c r="D194" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194" t="s">
+        <v>22</v>
+      </c>
+      <c r="G194">
+        <v>91119700</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>404</v>
+      </c>
+      <c r="B195" t="s">
+        <v>147</v>
+      </c>
+      <c r="C195" t="s">
+        <v>20</v>
+      </c>
+      <c r="D195" t="s">
+        <v>10</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="F195" t="s">
+        <v>22</v>
+      </c>
+      <c r="G195">
+        <v>19351985</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>405</v>
+      </c>
+      <c r="B196" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" t="s">
+        <v>147</v>
+      </c>
+      <c r="D196" t="s">
+        <v>10</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+      <c r="F196" t="s">
+        <v>22</v>
+      </c>
+      <c r="G196">
+        <v>29141472</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>406</v>
+      </c>
+      <c r="B197" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" t="s">
+        <v>147</v>
+      </c>
+      <c r="D197" t="s">
+        <v>10</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197" t="s">
+        <v>22</v>
+      </c>
+      <c r="G197">
+        <v>29115800</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>407</v>
+      </c>
+      <c r="B198" t="s">
+        <v>69</v>
+      </c>
+      <c r="C198" t="s">
+        <v>362</v>
+      </c>
+      <c r="D198" t="s">
+        <v>10</v>
+      </c>
+      <c r="E198">
+        <v>4</v>
+      </c>
+      <c r="F198" t="s">
+        <v>28</v>
+      </c>
+      <c r="G198">
+        <v>27039017</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>408</v>
+      </c>
+      <c r="B199" t="s">
+        <v>147</v>
+      </c>
+      <c r="C199" t="s">
+        <v>287</v>
+      </c>
+      <c r="D199" t="s">
+        <v>10</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+      <c r="F199" t="s">
+        <v>28</v>
+      </c>
+      <c r="G199">
+        <v>2000111594</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>409</v>
+      </c>
+      <c r="B200" t="s">
+        <v>124</v>
+      </c>
+      <c r="C200" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" t="s">
+        <v>10</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>22</v>
+      </c>
+      <c r="G200">
+        <v>2000024341</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>410</v>
+      </c>
+      <c r="B201" t="s">
+        <v>8</v>
+      </c>
+      <c r="C201" t="s">
+        <v>124</v>
+      </c>
+      <c r="D201" t="s">
+        <v>10</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="F201" t="s">
+        <v>22</v>
+      </c>
+      <c r="G201">
+        <v>14044150</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>411</v>
+      </c>
+      <c r="B202" t="s">
+        <v>147</v>
+      </c>
+      <c r="C202" t="s">
+        <v>303</v>
+      </c>
+      <c r="D202" t="s">
+        <v>10</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202" t="s">
+        <v>22</v>
+      </c>
+      <c r="G202">
+        <v>29186052</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>412</v>
+      </c>
+      <c r="B203" t="s">
+        <v>303</v>
+      </c>
+      <c r="C203" t="s">
+        <v>147</v>
+      </c>
+      <c r="D203" t="s">
+        <v>10</v>
+      </c>
+      <c r="E203">
+        <v>9</v>
+      </c>
+      <c r="F203" t="s">
+        <v>22</v>
+      </c>
+      <c r="G203">
+        <v>18077264</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>413</v>
+      </c>
+      <c r="B204" t="s">
+        <v>303</v>
+      </c>
+      <c r="C204" t="s">
+        <v>124</v>
+      </c>
+      <c r="D204" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204" t="s">
+        <v>22</v>
+      </c>
+      <c r="G204">
+        <v>91187791</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>414</v>
+      </c>
+      <c r="B205" t="s">
+        <v>124</v>
+      </c>
+      <c r="C205" t="s">
+        <v>303</v>
+      </c>
+      <c r="D205" t="s">
+        <v>10</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205" t="s">
+        <v>22</v>
+      </c>
+      <c r="G205">
+        <v>2000047226</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>415</v>
+      </c>
+      <c r="B206" t="s">
+        <v>124</v>
+      </c>
+      <c r="C206" t="s">
+        <v>303</v>
+      </c>
+      <c r="D206" t="s">
+        <v>10</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206" t="s">
+        <v>22</v>
+      </c>
+      <c r="G206">
+        <v>2000006186</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>416</v>
+      </c>
+      <c r="B207" t="s">
+        <v>124</v>
+      </c>
+      <c r="C207" t="s">
+        <v>303</v>
+      </c>
+      <c r="D207" t="s">
+        <v>10</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207" t="s">
+        <v>22</v>
+      </c>
+      <c r="G207">
+        <v>18108540</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>417</v>
+      </c>
+      <c r="B208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C208" t="s">
+        <v>21</v>
+      </c>
+      <c r="D208" t="s">
+        <v>418</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208" t="s">
+        <v>22</v>
+      </c>
+      <c r="G208">
+        <v>91207698</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>419</v>
+      </c>
+      <c r="B209" t="s">
+        <v>50</v>
+      </c>
+      <c r="C209" t="s">
+        <v>164</v>
+      </c>
+      <c r="D209" t="s">
+        <v>10</v>
+      </c>
+      <c r="E209">
+        <v>4</v>
+      </c>
+      <c r="F209" t="s">
+        <v>28</v>
+      </c>
+      <c r="G209">
+        <v>2000006104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A167:F223"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>225</v>
+      </c>
+      <c r="B167" t="s">
+        <v>226</v>
+      </c>
+      <c r="C167" t="s">
+        <v>227</v>
+      </c>
+      <c r="D167" t="s">
+        <v>228</v>
+      </c>
+      <c r="E167" t="s">
+        <v>229</v>
+      </c>
+      <c r="F167" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>46</v>
+      </c>
+      <c r="B168" t="s">
+        <v>231</v>
+      </c>
+      <c r="C168" t="s">
+        <v>232</v>
+      </c>
+      <c r="D168" t="s">
+        <v>233</v>
+      </c>
+      <c r="E168" s="1">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>234</v>
+      </c>
+      <c r="B169" t="s">
+        <v>235</v>
+      </c>
+      <c r="C169" t="s">
+        <v>236</v>
+      </c>
+      <c r="D169" t="s">
+        <v>237</v>
+      </c>
+      <c r="E169" s="1">
+        <v>44317</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>238</v>
+      </c>
+      <c r="B170" t="s">
+        <v>231</v>
+      </c>
+      <c r="C170" t="s">
+        <v>239</v>
+      </c>
+      <c r="D170" t="s">
+        <v>240</v>
+      </c>
+      <c r="E170" s="1">
+        <v>45549</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>61</v>
+      </c>
+      <c r="B172" t="s">
+        <v>241</v>
+      </c>
+      <c r="C172" t="s">
+        <v>242</v>
+      </c>
+      <c r="D172" t="s">
+        <v>243</v>
+      </c>
+      <c r="E172" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>244</v>
+      </c>
+      <c r="B173" t="s">
+        <v>245</v>
+      </c>
+      <c r="C173" t="s">
+        <v>246</v>
+      </c>
+      <c r="D173" t="s">
+        <v>246</v>
+      </c>
+      <c r="E173" s="1">
+        <v>43922</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>247</v>
+      </c>
+      <c r="C174" t="s">
+        <v>248</v>
+      </c>
+      <c r="D174" t="s">
+        <v>249</v>
+      </c>
+      <c r="E174" s="1">
+        <v>45781</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>98</v>
+      </c>
+      <c r="B175" t="s">
+        <v>250</v>
+      </c>
+      <c r="C175" t="s">
+        <v>251</v>
+      </c>
+      <c r="D175" t="s">
+        <v>251</v>
+      </c>
+      <c r="E175" s="1">
+        <v>44962</v>
+      </c>
+      <c r="F175" s="1">
+        <v>45544</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>124</v>
+      </c>
+      <c r="B176" t="s">
+        <v>231</v>
+      </c>
+      <c r="C176" t="s">
+        <v>252</v>
+      </c>
+      <c r="D176" t="s">
+        <v>253</v>
+      </c>
+      <c r="E176" s="1">
+        <v>45790</v>
+      </c>
+      <c r="F176" s="1">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>53</v>
+      </c>
+      <c r="B177" t="s">
+        <v>254</v>
+      </c>
+      <c r="C177" t="s">
+        <v>255</v>
+      </c>
+      <c r="D177" t="s">
+        <v>255</v>
+      </c>
+      <c r="E177" s="1">
+        <v>44501</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>199</v>
+      </c>
+      <c r="B178" t="s">
+        <v>256</v>
+      </c>
+      <c r="C178" t="s">
+        <v>257</v>
+      </c>
+      <c r="D178" t="s">
+        <v>258</v>
+      </c>
+      <c r="E178" s="1">
+        <v>45375</v>
+      </c>
+      <c r="F178" s="1">
+        <v>45845</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>13</v>
+      </c>
+      <c r="B179" t="s">
+        <v>259</v>
+      </c>
+      <c r="C179" t="s">
+        <v>260</v>
+      </c>
+      <c r="D179" t="s">
+        <v>261</v>
+      </c>
+      <c r="E179" s="1">
+        <v>44136</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>262</v>
+      </c>
+      <c r="B180" t="s">
+        <v>263</v>
+      </c>
+      <c r="C180" t="s">
+        <v>264</v>
+      </c>
+      <c r="D180" t="s">
+        <v>265</v>
+      </c>
+      <c r="E180" s="1">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>84</v>
+      </c>
+      <c r="B181" t="s">
+        <v>266</v>
+      </c>
+      <c r="C181" t="s">
+        <v>267</v>
+      </c>
+      <c r="D181" t="s">
+        <v>268</v>
+      </c>
+      <c r="E181" s="1">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>14</v>
+      </c>
+      <c r="B182" t="s">
+        <v>269</v>
+      </c>
+      <c r="C182" t="s">
+        <v>270</v>
+      </c>
+      <c r="D182" t="s">
+        <v>270</v>
+      </c>
+      <c r="E182" s="1">
+        <v>43952</v>
+      </c>
+      <c r="F182" s="1">
+        <v>45567</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>25</v>
+      </c>
+      <c r="B183" t="s">
+        <v>271</v>
+      </c>
+      <c r="C183" t="s">
+        <v>271</v>
+      </c>
+      <c r="D183" t="s">
+        <v>271</v>
+      </c>
+      <c r="E183" s="1">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>272</v>
+      </c>
+      <c r="B184" t="s">
+        <v>273</v>
+      </c>
+      <c r="C184" t="s">
+        <v>274</v>
+      </c>
+      <c r="D184" t="s">
+        <v>275</v>
+      </c>
+      <c r="E184" s="1">
+        <v>45234</v>
+      </c>
+      <c r="F184" s="1">
+        <v>45372</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>168</v>
+      </c>
+      <c r="B185" t="s">
+        <v>276</v>
+      </c>
+      <c r="C185" t="s">
+        <v>277</v>
+      </c>
+      <c r="D185" t="s">
+        <v>277</v>
+      </c>
+      <c r="E185" s="1">
+        <v>45211</v>
+      </c>
+      <c r="F185" s="1">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>163</v>
+      </c>
+      <c r="B186" t="s">
+        <v>278</v>
+      </c>
+      <c r="C186" t="s">
+        <v>279</v>
+      </c>
+      <c r="D186" t="s">
+        <v>280</v>
+      </c>
+      <c r="E186" s="1">
+        <v>44348</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>136</v>
+      </c>
+      <c r="B187" t="s">
+        <v>281</v>
+      </c>
+      <c r="C187" t="s">
+        <v>282</v>
+      </c>
+      <c r="D187" t="s">
+        <v>283</v>
+      </c>
+      <c r="E187" s="1">
+        <v>45600</v>
+      </c>
+      <c r="F187" s="1">
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>284</v>
+      </c>
+      <c r="B188" t="s">
+        <v>285</v>
+      </c>
+      <c r="C188" t="s">
+        <v>286</v>
+      </c>
+      <c r="D188" t="s">
+        <v>286</v>
+      </c>
+      <c r="E188" s="1">
+        <v>45609</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>287</v>
+      </c>
+      <c r="B189" t="s">
+        <v>273</v>
+      </c>
+      <c r="C189" t="s">
+        <v>288</v>
+      </c>
+      <c r="D189" t="s">
+        <v>289</v>
+      </c>
+      <c r="E189" s="1">
+        <v>45084</v>
+      </c>
+      <c r="F189" s="1">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>290</v>
+      </c>
+      <c r="B190" t="s">
+        <v>291</v>
+      </c>
+      <c r="C190" t="s">
+        <v>292</v>
+      </c>
+      <c r="D190" t="s">
+        <v>291</v>
+      </c>
+      <c r="E190" s="1">
+        <v>43922</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>16</v>
+      </c>
+      <c r="B191" t="s">
+        <v>293</v>
+      </c>
+      <c r="C191" t="s">
+        <v>293</v>
+      </c>
+      <c r="D191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E191" s="1">
+        <v>44591</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>175</v>
+      </c>
+      <c r="B192" t="s">
+        <v>294</v>
+      </c>
+      <c r="C192" t="s">
+        <v>295</v>
+      </c>
+      <c r="D192" t="s">
+        <v>295</v>
+      </c>
+      <c r="E192" s="1">
+        <v>45341</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>296</v>
+      </c>
+      <c r="B193" t="s">
+        <v>297</v>
+      </c>
+      <c r="C193" t="s">
+        <v>298</v>
+      </c>
+      <c r="D193" t="s">
+        <v>297</v>
+      </c>
+      <c r="E193" s="1">
+        <v>44910</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>127</v>
+      </c>
+      <c r="B194" t="s">
+        <v>299</v>
+      </c>
+      <c r="C194" t="s">
+        <v>299</v>
+      </c>
+      <c r="D194" t="s">
+        <v>299</v>
+      </c>
+      <c r="E194" s="1">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>18</v>
+      </c>
+      <c r="B195" t="s">
+        <v>300</v>
+      </c>
+      <c r="C195" t="s">
+        <v>301</v>
+      </c>
+      <c r="D195" t="s">
+        <v>302</v>
+      </c>
+      <c r="E195" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>303</v>
+      </c>
+      <c r="B196" t="s">
+        <v>304</v>
+      </c>
+      <c r="C196" t="s">
+        <v>305</v>
+      </c>
+      <c r="D196" t="s">
+        <v>304</v>
+      </c>
+      <c r="E196" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>69</v>
+      </c>
+      <c r="B197" t="s">
+        <v>306</v>
+      </c>
+      <c r="C197" t="s">
+        <v>307</v>
+      </c>
+      <c r="D197" t="s">
+        <v>307</v>
+      </c>
+      <c r="E197" s="1">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>93</v>
+      </c>
+      <c r="B198" t="s">
+        <v>308</v>
+      </c>
+      <c r="C198" t="s">
+        <v>309</v>
+      </c>
+      <c r="D198" t="s">
+        <v>309</v>
+      </c>
+      <c r="E198" s="1">
+        <v>45668</v>
+      </c>
+      <c r="F198" s="1">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>211</v>
+      </c>
+      <c r="B199" t="s">
+        <v>310</v>
+      </c>
+      <c r="C199" t="s">
+        <v>311</v>
+      </c>
+      <c r="D199" t="s">
+        <v>312</v>
+      </c>
+      <c r="E199" s="1">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" t="s">
+        <v>313</v>
+      </c>
+      <c r="C200" t="s">
+        <v>314</v>
+      </c>
+      <c r="D200" t="s">
+        <v>315</v>
+      </c>
+      <c r="E200" s="1">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>50</v>
+      </c>
+      <c r="B201" t="s">
+        <v>254</v>
+      </c>
+      <c r="C201" t="s">
+        <v>316</v>
+      </c>
+      <c r="D201" t="s">
+        <v>317</v>
+      </c>
+      <c r="E201" s="1">
+        <v>44075</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" t="s">
+        <v>318</v>
+      </c>
+      <c r="C202" t="s">
+        <v>319</v>
+      </c>
+      <c r="D202" t="s">
+        <v>320</v>
+      </c>
+      <c r="E202" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>26</v>
+      </c>
+      <c r="B203" t="s">
+        <v>321</v>
+      </c>
+      <c r="C203" t="s">
+        <v>322</v>
+      </c>
+      <c r="D203" t="s">
+        <v>323</v>
+      </c>
+      <c r="E203" s="1">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>151</v>
+      </c>
+      <c r="B204" t="s">
+        <v>324</v>
+      </c>
+      <c r="C204" t="s">
+        <v>325</v>
+      </c>
+      <c r="D204" t="s">
+        <v>326</v>
+      </c>
+      <c r="E204" s="1">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>21</v>
+      </c>
+      <c r="B205" t="s">
+        <v>327</v>
+      </c>
+      <c r="C205" t="s">
+        <v>328</v>
+      </c>
+      <c r="D205" t="s">
+        <v>328</v>
+      </c>
+      <c r="E205" s="1">
+        <v>45470</v>
+      </c>
+      <c r="F205" s="1">
+        <v>45916</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>329</v>
+      </c>
+      <c r="B206" t="s">
+        <v>330</v>
+      </c>
+      <c r="C206" t="s">
+        <v>330</v>
+      </c>
+      <c r="D206" t="s">
+        <v>330</v>
+      </c>
+      <c r="E206" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>88</v>
+      </c>
+      <c r="B207" t="s">
+        <v>331</v>
+      </c>
+      <c r="C207" t="s">
+        <v>332</v>
+      </c>
+      <c r="D207" t="s">
+        <v>333</v>
+      </c>
+      <c r="E207" s="1">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>334</v>
+      </c>
+      <c r="B208" t="s">
+        <v>335</v>
+      </c>
+      <c r="C208" t="s">
+        <v>336</v>
+      </c>
+      <c r="D208" t="s">
+        <v>337</v>
+      </c>
+      <c r="E208" s="1">
+        <v>43952</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>45</v>
+      </c>
+      <c r="B209" t="s">
+        <v>338</v>
+      </c>
+      <c r="C209" t="s">
+        <v>339</v>
+      </c>
+      <c r="D209" t="s">
+        <v>340</v>
+      </c>
+      <c r="E209" s="1">
+        <v>43983</v>
+      </c>
+      <c r="F209" s="1">
+        <v>45013</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>171</v>
+      </c>
+      <c r="B210" t="s">
+        <v>341</v>
+      </c>
+      <c r="C210" t="s">
+        <v>342</v>
+      </c>
+      <c r="D210" t="s">
+        <v>343</v>
+      </c>
+      <c r="E210" s="1">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>59</v>
+      </c>
+      <c r="B211" t="s">
+        <v>344</v>
+      </c>
+      <c r="C211" t="s">
+        <v>345</v>
+      </c>
+      <c r="D211" t="s">
+        <v>346</v>
+      </c>
+      <c r="E211" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>67</v>
+      </c>
+      <c r="B212" t="s">
+        <v>347</v>
+      </c>
+      <c r="C212" t="s">
+        <v>348</v>
+      </c>
+      <c r="D212" t="s">
+        <v>348</v>
+      </c>
+      <c r="E212" s="1">
+        <v>44013</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>349</v>
+      </c>
+      <c r="B213" t="s">
+        <v>350</v>
+      </c>
+      <c r="C213" t="s">
+        <v>351</v>
+      </c>
+      <c r="D213" t="s">
+        <v>352</v>
+      </c>
+      <c r="E213" s="1">
+        <v>44228</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>353</v>
+      </c>
+      <c r="B214" t="s">
+        <v>354</v>
+      </c>
+      <c r="C214" t="s">
+        <v>355</v>
+      </c>
+      <c r="D214" t="s">
+        <v>356</v>
+      </c>
+      <c r="E214" s="1">
+        <v>44075</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>203</v>
+      </c>
+      <c r="B215" t="s">
+        <v>357</v>
+      </c>
+      <c r="C215" t="s">
+        <v>358</v>
+      </c>
+      <c r="D215" t="s">
+        <v>359</v>
+      </c>
+      <c r="E215" s="1">
+        <v>44136</v>
+      </c>
+      <c r="F215" s="1">
+        <v>45201</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>20</v>
+      </c>
+      <c r="B216" t="s">
+        <v>360</v>
+      </c>
+      <c r="C216" t="s">
+        <v>361</v>
+      </c>
+      <c r="D216" t="s">
+        <v>360</v>
+      </c>
+      <c r="E216" s="1">
+        <v>44440</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>362</v>
+      </c>
+      <c r="B217" t="s">
+        <v>363</v>
+      </c>
+      <c r="C217" t="s">
+        <v>364</v>
+      </c>
+      <c r="D217" t="s">
+        <v>364</v>
+      </c>
+      <c r="E217" s="1">
+        <v>44197</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>164</v>
+      </c>
+      <c r="B218" t="s">
+        <v>365</v>
+      </c>
+      <c r="C218" t="s">
+        <v>366</v>
+      </c>
+      <c r="D218" t="s">
+        <v>367</v>
+      </c>
+      <c r="E218" s="1">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>147</v>
+      </c>
+      <c r="B219" t="s">
+        <v>368</v>
+      </c>
+      <c r="C219" t="s">
+        <v>369</v>
+      </c>
+      <c r="D219" t="s">
+        <v>370</v>
+      </c>
+      <c r="E219" s="1">
+        <v>44136</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>371</v>
+      </c>
+      <c r="B220" t="s">
+        <v>372</v>
+      </c>
+      <c r="C220" t="s">
+        <v>373</v>
+      </c>
+      <c r="D220" t="s">
+        <v>374</v>
+      </c>
+      <c r="E220" s="1">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>39</v>
+      </c>
+      <c r="B221" t="s">
+        <v>375</v>
+      </c>
+      <c r="C221" t="s">
+        <v>376</v>
+      </c>
+      <c r="D221" t="s">
+        <v>377</v>
+      </c>
+      <c r="E221" s="1">
+        <v>45778</v>
+      </c>
+      <c r="F221" s="1">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>378</v>
+      </c>
+      <c r="B222" t="s">
+        <v>379</v>
+      </c>
+      <c r="C222" t="s">
+        <v>380</v>
+      </c>
+      <c r="D222" t="s">
+        <v>381</v>
+      </c>
+      <c r="E222" s="1">
+        <v>43891</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>31</v>
+      </c>
+      <c r="B223" t="s">
+        <v>382</v>
+      </c>
+      <c r="C223" t="s">
+        <v>383</v>
+      </c>
+      <c r="D223" t="s">
+        <v>383</v>
+      </c>
+      <c r="E223" s="1">
+        <v>45000</v>
+      </c>
+      <c r="F223" s="1">
+        <v>45780</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>